--- a/DataTables/Datas/#MultiLanguageText.xlsx
+++ b/DataTables/Datas/#MultiLanguageText.xlsx
@@ -8,24 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Games\Takeover\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B8E8F0-4FCE-4D2D-9360-E7975935C606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBF8720-FE01-4B47-8824-5E7F4A82D27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="战役数据" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="106">
   <si>
     <t>##var</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -339,6 +351,76 @@
   <si>
     <t>Town</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击开始</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰谷神教</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>西利亚公国</t>
+  </si>
+  <si>
+    <t>深红部落</t>
+  </si>
+  <si>
+    <t>瑞弗埃达斯帝国</t>
+  </si>
+  <si>
+    <t>选择战役</t>
+  </si>
+  <si>
+    <t>冰谷神教是反叛者。
+教会的士兵兵团
+不擅长战斗，
+但枪支、魔法
+以及坚持不懈
+使教会更加强大。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>西利亚的战士
+天下闻名，
+特别是它的步兵
+以及上帝的教会
+传扬的神圣魔法
+使他们更加强大。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>深红部落的领土
+是一片残酷野蛮的大地。
+部落的骑兵清空
+挡道的一切事物，
+以及部落的萨满
+渴望参透黑暗魔法
+的秘密。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回</t>
+  </si>
+  <si>
+    <t>瑞弗埃达斯帝国的描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大敌当前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西利亚公国位于西边的岛屿上，他几乎没有被欧洲大陆上的麻烦事所波及到过.但现在他们过来了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混乱</t>
+  </si>
+  <si>
+    <t>深红部落在很久之前被帝国征服，但他们从没真正屈服.混乱重新降临瑞弗埃达斯.这些野蛮人趁机试图占领我们的领土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -399,7 +481,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -407,12 +489,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -423,7 +520,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -705,13 +807,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="8.6640625" style="4"/>
-    <col min="4" max="4" width="26.08203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="19.9140625" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="8.6640625" style="4"/>
+    <col min="1" max="1" width="8.6640625" style="5"/>
+    <col min="2" max="2" width="19.58203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="5"/>
+    <col min="4" max="4" width="26.08203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="19.9140625" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -1176,36 +1280,124 @@
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="5" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="5" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B47" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B48" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B49" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B50" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B51" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B52" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B54" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B55" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B56" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B57" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1217,4 +1409,111 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87C8518-ECE7-4254-BCFD-6101FD173011}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="6"/>
+    <col min="2" max="2" width="20.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="6"/>
+    <col min="4" max="4" width="24.75" style="6" customWidth="1"/>
+    <col min="5" max="5" width="27.25" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B7" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B8" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D1" r:id="rId1" xr:uid="{AF0E4DB4-01EB-4E7F-AE29-CBBE11C48061}"/>
+    <hyperlink ref="E1" r:id="rId2" xr:uid="{9A81B6F3-43A2-4D9C-977A-4DC72BF12009}"/>
+    <hyperlink ref="C1" r:id="rId3" display="text@ChineseSimplified" xr:uid="{ECD815E1-A88D-4EBC-954D-2FFEEDDEC53A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DataTables/Datas/#MultiLanguageText.xlsx
+++ b/DataTables/Datas/#MultiLanguageText.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17055" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="115">
   <si>
     <t>##var</t>
   </si>
@@ -377,6 +377,18 @@
   </si>
   <si>
     <t>关卡5</t>
+  </si>
+  <si>
+    <t>绿色战役</t>
+  </si>
+  <si>
+    <t>蓝色战役</t>
+  </si>
+  <si>
+    <t>红色战役</t>
+  </si>
+  <si>
+    <t>紫色战役</t>
   </si>
 </sst>
 </file>
@@ -389,7 +401,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,13 +421,6 @@
       <color theme="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -880,150 +885,150 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1037,6 +1042,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1913,10 +1922,10 @@
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" spans="2:4">
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="9" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1966,7 +1975,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8.66666666666667" style="1"/>
@@ -2115,6 +2124,50 @@
         <v>110</v>
       </c>
     </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D1" r:id="rId1" display="text@zh-Hans"/>

--- a/DataTables/Datas/#MultiLanguageText.xlsx
+++ b/DataTables/Datas/#MultiLanguageText.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17055" activeTab="1"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="116">
   <si>
     <t>##var</t>
   </si>
@@ -389,6 +389,9 @@
   </si>
   <si>
     <t>紫色战役</t>
+  </si>
+  <si>
+    <t>农场</t>
   </si>
 </sst>
 </file>
@@ -1975,7 +1978,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8.66666666666667" style="1"/>
@@ -2168,6 +2171,17 @@
         <v>114</v>
       </c>
     </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D1" r:id="rId1" display="text@zh-Hans"/>
